--- a/desplazamiento-alt.xlsx
+++ b/desplazamiento-alt.xlsx
@@ -420,10 +420,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="7" style="0" width="12.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="10.85"/>
@@ -1856,7 +1856,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -3280,7 +3280,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z23"/>
-  <sheetFormatPr defaultColWidth="10.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -4884,7 +4884,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:N53"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
@@ -6701,7 +6701,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B4:N55"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="0" t="s">
@@ -8518,7 +8518,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B3:M54"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="0" t="s">
